--- a/Bao cao/VCI/VCI_Model_2026-07-11.xlsx
+++ b/Bao cao/VCI/VCI_Model_2026-07-11.xlsx
@@ -25,6 +25,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_PE_PB_History" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Segment_Quarterly" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_Peer_Benchmark" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_FVTPL_Composition" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -172,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -244,6 +245,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11478,7 +11482,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>0.0103</v>
+        <v>0.0104</v>
       </c>
       <c r="C26" s="7" t="n"/>
     </row>
@@ -11608,19 +11612,19 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>-73.90000000000001</v>
+        <v>-139.4</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>-36.9</v>
+        <v>-69.7</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>36.9</v>
+        <v>69.7</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>73.90000000000001</v>
+        <v>139.4</v>
       </c>
     </row>
     <row r="5">
@@ -11630,19 +11634,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>-0.042</v>
+        <v>-0.079</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.039</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.021</v>
+        <v>0.039</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.042</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -12980,7 +12984,7 @@
       </c>
       <c r="B2" s="49" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Vietcap vận hành mô hình 5 mảng: Môi giới, Cho vay Margin, Tự doanh (FVTPL), IB+Lưu ký, Quản lý quỹ. Mảng đóng góp lớn nhất hiện tại: Cho vay Margin (42.8% DT).</t>
+          <t>Công ty Cổ phần Chứng khoán Vietcap vận hành mô hình 5 mảng: Môi giới, Cho vay Margin, Tự doanh (FVTPL), IB+Lưu ký, Quản lý quỹ. Mảng đóng góp lớn nhất hiện tại: Cho vay Margin (42.5% DT).</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -13014,7 +13018,7 @@
       </c>
       <c r="B4" s="49" t="inlineStr">
         <is>
-          <t>Upside +25.7% so với giá hiện tại theo mô hình P/B (60%) + P/E (40%).</t>
+          <t>Upside +25.8% so với giá hiện tại theo mô hình P/B (60%) + P/E (40%).</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -13134,13 +13138,13 @@
         <v>4980.201525108</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>3633.4</v>
+        <v>3662.2</v>
       </c>
       <c r="H2" s="23" t="n">
-        <v>3175.8</v>
+        <v>3217.8</v>
       </c>
       <c r="I2" s="23" t="n">
-        <v>3404.8</v>
+        <v>3449.7</v>
       </c>
     </row>
     <row r="3">
@@ -13165,13 +13169,13 @@
         <v>1341.954507258</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>1457.6</v>
+        <v>1466.5</v>
       </c>
       <c r="H3" s="23" t="n">
-        <v>1301.6</v>
+        <v>1318.8</v>
       </c>
       <c r="I3" s="23" t="n">
-        <v>1395.5</v>
+        <v>1413.9</v>
       </c>
     </row>
     <row r="4">
@@ -13196,13 +13200,13 @@
         <v>1165</v>
       </c>
       <c r="G4" s="23" t="n">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="H4" s="23" t="n">
-        <v>1130</v>
+        <v>1145</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>1211</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="5">
@@ -13227,13 +13231,13 @@
         <v>15630</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>16642</v>
+        <v>16649</v>
       </c>
       <c r="H5" s="23" t="n">
-        <v>17546</v>
+        <v>17564</v>
       </c>
       <c r="I5" s="23" t="n">
-        <v>18515</v>
+        <v>18546</v>
       </c>
     </row>
     <row r="6">
@@ -13258,13 +13262,13 @@
         <v>18009.896539949</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>19175.976539949</v>
+        <v>19183.096539949</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>20217.256539949</v>
+        <v>20238.136539949</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>21333.656539949</v>
+        <v>21369.256539949</v>
       </c>
     </row>
     <row r="7">
@@ -13289,13 +13293,13 @@
         <v>7.45</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>7.6</v>
+        <v>7.64</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>6.44</v>
+        <v>6.52</v>
       </c>
       <c r="I7" s="53" t="n">
-        <v>6.54</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="8">
@@ -13320,13 +13324,13 @@
         <v>20.99</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>19.33</v>
+        <v>19.21</v>
       </c>
       <c r="H8" s="34" t="n">
-        <v>21.64</v>
+        <v>21.35</v>
       </c>
       <c r="I8" s="34" t="n">
-        <v>20.19</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="9">
@@ -15570,6 +15574,876 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="3" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>CƠ CẤU &amp; HIỆU QUẢ DANH MỤC TỰ DOANH FVTPL/AFS — VCI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Nguồn: thuyết minh BCTC hợp nhất (mục 'Tài sản tài chính ghi nhận thông qua lãi/lỗ FVTPL' / 'sẵn sàng để bán AFS'), trích trực tiếp — KHÔNG ước tính. Đơn vị: tỷ VND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>1. CƠ CẤU DANH MỤC THEO NHÓM TÀI SẢN (Giá trị hợp lý, tỷ VND)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm tài sản</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2022(N)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2023(N)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2024Q4</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Cổ phiếu niêm yết/UPCoM</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="C6" s="57" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="D6" s="57" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>753.8</v>
+      </c>
+      <c r="F6" s="57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G6" s="57" t="n">
+        <v>197.3</v>
+      </c>
+      <c r="H6" s="57" t="n">
+        <v>823.8</v>
+      </c>
+      <c r="I6" s="57" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="J6" s="57" t="n">
+        <v>156.4</v>
+      </c>
+      <c r="K6" s="57" t="n">
+        <v>45</v>
+      </c>
+      <c r="L6" s="57" t="n">
+        <v>549.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Cổ phiếu chưa niêm yết</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Trái phiếu</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="n">
+        <v>598.6</v>
+      </c>
+      <c r="C8" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="57" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="F8" s="57" t="n">
+        <v>452.5</v>
+      </c>
+      <c r="G8" s="57" t="n">
+        <v>628.6</v>
+      </c>
+      <c r="H8" s="57" t="n">
+        <v>271.9</v>
+      </c>
+      <c r="I8" s="57" t="n">
+        <v>713.5</v>
+      </c>
+      <c r="J8" s="57" t="n">
+        <v>443</v>
+      </c>
+      <c r="K8" s="57" t="n">
+        <v>2135.2</v>
+      </c>
+      <c r="L8" s="57" t="n">
+        <v>1316.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Chứng chỉ quỹ (ETF+Quỹ mở)</t>
+        </is>
+      </c>
+      <c r="B9" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="57" t="n">
+        <v>213</v>
+      </c>
+      <c r="F9" s="57" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G9" s="57" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H9" s="57" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="I9" s="57" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J9" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="57" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="L9" s="57" t="n">
+        <v>173.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Chứng chỉ tiền gửi</t>
+        </is>
+      </c>
+      <c r="B10" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="57" t="n">
+        <v>357</v>
+      </c>
+      <c r="E10" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="57" t="n">
+        <v>511.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B11" s="30">
+        <f>SUM(B6:B10)</f>
+        <v/>
+      </c>
+      <c r="C11" s="30">
+        <f>SUM(C6:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="30">
+        <f>SUM(D6:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="30">
+        <f>SUM(E6:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
+        <f>SUM(F6:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="30">
+        <f>SUM(G6:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="30">
+        <f>SUM(H6:H10)</f>
+        <v/>
+      </c>
+      <c r="I11" s="30">
+        <f>SUM(I6:I10)</f>
+        <v/>
+      </c>
+      <c r="J11" s="30">
+        <f>SUM(J6:J10)</f>
+        <v/>
+      </c>
+      <c r="K11" s="30">
+        <f>SUM(K6:K10)</f>
+        <v/>
+      </c>
+      <c r="L11" s="30">
+        <f>SUM(L6:L10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>2. LÃI/LỖ ĐÁNH GIÁ LẠI THEO NHÓM TÀI SẢN (tỷ VND, tại thời điểm báo cáo so với giá gốc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm tài sản</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2022(N)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2023(N)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2024Q4</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Cổ phiếu niêm yết/UPCoM (ròng)</t>
+        </is>
+      </c>
+      <c r="B16" s="57" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="C16" s="57" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="D16" s="57" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E16" s="57" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F16" s="57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="57" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="H16" s="57" t="n"/>
+      <c r="I16" s="57" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="J16" s="57" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="K16" s="57" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L16" s="57" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Cổ phiếu chưa niêm yết (ròng)</t>
+        </is>
+      </c>
+      <c r="B17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Trái phiếu (ròng)</t>
+        </is>
+      </c>
+      <c r="B18" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="57" t="n"/>
+      <c r="I18" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K18" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Chứng chỉ quỹ (ETF+Quỹ mở) (ròng)</t>
+        </is>
+      </c>
+      <c r="B19" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F19" s="57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G19" s="57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H19" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L19" s="57" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Chứng chỉ tiền gửi (ròng)</t>
+        </is>
+      </c>
+      <c r="B20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>3. DANH MỤC CỔ PHIẾU NIÊM YẾT CỤ THỂ ĐANG NẮM GIỮ (Giá trị hợp lý, tỷ VND)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Mã CP</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2022(N)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2023(N)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2024(N)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>2025(N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="B25" s="57" t="n">
+        <v>1617.9</v>
+      </c>
+      <c r="C25" s="57" t="n">
+        <v>2166.2</v>
+      </c>
+      <c r="D25" s="57" t="n">
+        <v>2117.6</v>
+      </c>
+      <c r="E25" s="57" t="n">
+        <v>2201.6</v>
+      </c>
+      <c r="F25" s="57" t="n">
+        <v>1945.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>KDH</t>
+        </is>
+      </c>
+      <c r="B26" s="57" t="n">
+        <v>357</v>
+      </c>
+      <c r="C26" s="57" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D26" s="57" t="n">
+        <v>1183.8</v>
+      </c>
+      <c r="E26" s="57" t="n">
+        <v>1016.7</v>
+      </c>
+      <c r="F26" s="57" t="n">
+        <v>1065.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>MBB</t>
+        </is>
+      </c>
+      <c r="B27" s="57" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="C27" s="57" t="n">
+        <v>246.6</v>
+      </c>
+      <c r="D27" s="57" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E27" s="57" t="n">
+        <v>222.6</v>
+      </c>
+      <c r="F27" s="57" t="n">
+        <v>450.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>MSN</t>
+        </is>
+      </c>
+      <c r="B28" s="57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C28" s="57" t="n">
+        <v>236.3</v>
+      </c>
+      <c r="D28" s="57" t="n"/>
+      <c r="E28" s="57" t="n">
+        <v>78</v>
+      </c>
+      <c r="F28" s="57" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>PNJ</t>
+        </is>
+      </c>
+      <c r="B29" s="57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C29" s="57" t="n">
+        <v>234.1</v>
+      </c>
+      <c r="D29" s="57" t="n"/>
+      <c r="E29" s="57" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="F29" s="57" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>FPT</t>
+        </is>
+      </c>
+      <c r="B30" s="57" t="n"/>
+      <c r="C30" s="57" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="D30" s="57" t="n">
+        <v>695.4</v>
+      </c>
+      <c r="E30" s="57" t="n">
+        <v>548.7</v>
+      </c>
+      <c r="F30" s="57" t="n">
+        <v>588.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>STB</t>
+        </is>
+      </c>
+      <c r="B31" s="57" t="n"/>
+      <c r="C31" s="57" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="D31" s="57" t="n"/>
+      <c r="E31" s="57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F31" s="57" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>MCH</t>
+        </is>
+      </c>
+      <c r="B32" s="57" t="n"/>
+      <c r="C32" s="57" t="n"/>
+      <c r="D32" s="57" t="n">
+        <v>569.7</v>
+      </c>
+      <c r="E32" s="57" t="n"/>
+      <c r="F32" s="57" t="n">
+        <v>2529.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>TDM</t>
+        </is>
+      </c>
+      <c r="B33" s="57" t="n"/>
+      <c r="C33" s="57" t="n"/>
+      <c r="D33" s="57" t="n">
+        <v>772.4</v>
+      </c>
+      <c r="E33" s="57" t="n">
+        <v>760</v>
+      </c>
+      <c r="F33" s="57" t="n">
+        <v>884.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Khac</t>
+        </is>
+      </c>
+      <c r="B34" s="57" t="n">
+        <v>681.8</v>
+      </c>
+      <c r="C34" s="57" t="n">
+        <v>1556.6</v>
+      </c>
+      <c r="D34" s="57" t="n">
+        <v>1668.1</v>
+      </c>
+      <c r="E34" s="57" t="n">
+        <v>2060.4</v>
+      </c>
+      <c r="F34" s="57" t="n">
+        <v>2959.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -15619,7 +16493,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Fallback (manual)</t>
+          <t>Cache lần chạy trước (2026-07-11 19:01)</t>
         </is>
       </c>
     </row>
@@ -15758,7 +16632,7 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>32119</v>
+        <v>32133</v>
       </c>
     </row>
     <row r="11">
@@ -15768,7 +16642,7 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>18229</v>
+        <v>18344</v>
       </c>
     </row>
     <row r="12">
@@ -15801,7 +16675,7 @@
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>30730</v>
+        <v>30754</v>
       </c>
     </row>
     <row r="16">
@@ -15811,7 +16685,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.257</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="17">
@@ -16279,17 +17153,17 @@
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="21" t="n">
-        <v>0.5</v>
+        <v>0.2007</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>0.5</v>
+        <v>0.2007</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>0.5</v>
+        <v>0.2007</v>
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>⚠ GIẢ ĐỊNH THỦ CÔNG — chưa có data/fvtpl_holdings/VCI.json (thuyết minh cơ cấu danh mục FVTPL chi tiết theo loại tài sản), nên dùng bảng giả định chung theo ticker/ngành. Mặc định chỉ mang tính khởi điểm — BẮT BUỘC điều chỉnh theo thuyết minh BCTC thực tế nếu có. Đối chiếu với dòng 'Hiệu suất Tự doanh THỰC TẾ lịch sử' bên dưới để hiệu chỉnh.</t>
+          <t>✓ CƠ CẤU THẬT — trích trực tiếp từ thuyết minh BCTC (data/fvtpl_holdings/VCI.json, kỳ gần nhất, xem sheet 16_FVTPL_Composition) — KHÔNG phải giả định. Cập nhật lại khi có kỳ báo cáo mới hơn (chạy lại quy trình thu thập dữ liệu FVTPL).</t>
         </is>
       </c>
     </row>
@@ -16305,17 +17179,17 @@
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="21" t="n">
-        <v>0.35</v>
+        <v>0.5162</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>0.35</v>
+        <v>0.5162</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>0.35</v>
+        <v>0.5162</v>
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>⚠ GIẢ ĐỊNH THỦ CÔNG — chưa có data/fvtpl_holdings/VCI.json (thuyết minh cơ cấu danh mục FVTPL chi tiết theo loại tài sản), nên dùng bảng giả định chung theo ticker/ngành. Mặc định chỉ mang tính khởi điểm — BẮT BUỘC điều chỉnh theo thuyết minh BCTC thực tế nếu có. Đối chiếu với dòng 'Hiệu suất Tự doanh THỰC TẾ lịch sử' bên dưới để hiệu chỉnh.</t>
+          <t>✓ CƠ CẤU THẬT — trích trực tiếp từ thuyết minh BCTC (data/fvtpl_holdings/VCI.json, kỳ gần nhất, xem sheet 16_FVTPL_Composition) — KHÔNG phải giả định. Cập nhật lại khi có kỳ báo cáo mới hơn (chạy lại quy trình thu thập dữ liệu FVTPL).</t>
         </is>
       </c>
     </row>
@@ -16331,17 +17205,17 @@
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="21" t="n">
-        <v>0.15</v>
+        <v>0.2832</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>0.15</v>
+        <v>0.2832</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>0.15</v>
+        <v>0.2832</v>
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>⚠ GIẢ ĐỊNH THỦ CÔNG — chưa có data/fvtpl_holdings/VCI.json (thuyết minh cơ cấu danh mục FVTPL chi tiết theo loại tài sản), nên dùng bảng giả định chung theo ticker/ngành. Mặc định chỉ mang tính khởi điểm — BẮT BUỘC điều chỉnh theo thuyết minh BCTC thực tế nếu có. Đối chiếu với dòng 'Hiệu suất Tự doanh THỰC TẾ lịch sử' bên dưới để hiệu chỉnh.</t>
+          <t>✓ CƠ CẤU THẬT — trích trực tiếp từ thuyết minh BCTC (data/fvtpl_holdings/VCI.json, kỳ gần nhất, xem sheet 16_FVTPL_Composition) — KHÔNG phải giả định. Cập nhật lại khi có kỳ báo cáo mới hơn (chạy lại quy trình thu thập dữ liệu FVTPL).</t>
         </is>
       </c>
     </row>
@@ -16400,7 +17274,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>R_VNI — Biến động kỳ vọng VN-Index (%/năm)</t>
+          <t>R_VNI — Lợi suất kỳ vọng CP+Chứng chỉ quỹ (%/năm)</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
@@ -16409,17 +17283,17 @@
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.1437</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.1437</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.1437</v>
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>⚠ KHÔNG kiểm chứng được — kỳ vọng lợi suất tương lai mang tính chủ quan, không có "đúng/sai". Đối chiếu với COE (sheet 00_COE) hoặc quan điểm thị trường riêng khi điều chỉnh</t>
+          <t>✓ NHẤT QUÁN CAPM — dùng ĐÚNG COE (sheet 00_COE = Rf+β×ERP+α của chính ticker này) làm lợi suất kỳ vọng phần rủi ro cổ phiếu, thay vì con số 10% chủ quan trước đây — cùng suất chiết khấu với mô hình định giá.</t>
         </is>
       </c>
     </row>
@@ -18536,13 +19410,13 @@
         <v>16064.5</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>22431.9</v>
+        <v>22424.7</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>25550.6</v>
+        <v>25529.7</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>28049.2</v>
+        <v>28013.6</v>
       </c>
     </row>
     <row r="8">
@@ -18637,13 +19511,13 @@
         <v>18009.9</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>19176</v>
+        <v>19183.1</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>20217.3</v>
+        <v>20238.1</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>21333.7</v>
+        <v>21369.3</v>
       </c>
     </row>
     <row r="12">

--- a/Bao cao/VCI/VCI_Model_2026-07-11.xlsx
+++ b/Bao cao/VCI/VCI_Model_2026-07-11.xlsx
@@ -11482,7 +11482,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>0.0104</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="C26" s="7" t="n"/>
     </row>
@@ -11612,19 +11612,19 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>-139.4</v>
+        <v>-393.7</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>-69.7</v>
+        <v>-196.9</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>69.7</v>
+        <v>196.9</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>139.4</v>
+        <v>393.7</v>
       </c>
     </row>
     <row r="5">
@@ -11634,19 +11634,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.273</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-0.039</v>
+        <v>-0.137</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.039</v>
+        <v>0.137</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.079</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -12182,35 +12182,35 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <f>'03_Revenue_Model'!B22</f>
+        <f>'03_Revenue_Model'!B25</f>
         <v/>
       </c>
       <c r="C5" s="8">
-        <f>'03_Revenue_Model'!C22</f>
+        <f>'03_Revenue_Model'!C25</f>
         <v/>
       </c>
       <c r="D5" s="8">
-        <f>'03_Revenue_Model'!D22</f>
+        <f>'03_Revenue_Model'!D25</f>
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>'03_Revenue_Model'!E22</f>
+        <f>'03_Revenue_Model'!E25</f>
         <v/>
       </c>
       <c r="F5" s="8">
-        <f>'03_Revenue_Model'!F22</f>
+        <f>'03_Revenue_Model'!F25</f>
         <v/>
       </c>
       <c r="G5" s="8">
-        <f>'03_Revenue_Model'!G22</f>
+        <f>'03_Revenue_Model'!G25</f>
         <v/>
       </c>
       <c r="H5" s="8">
-        <f>'03_Revenue_Model'!H22</f>
+        <f>'03_Revenue_Model'!H25</f>
         <v/>
       </c>
       <c r="I5" s="8">
-        <f>'03_Revenue_Model'!I22</f>
+        <f>'03_Revenue_Model'!I25</f>
         <v/>
       </c>
     </row>
@@ -12221,35 +12221,35 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>'03_Revenue_Model'!B23</f>
+        <f>'03_Revenue_Model'!B26</f>
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>'03_Revenue_Model'!C23</f>
+        <f>'03_Revenue_Model'!C26</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>'03_Revenue_Model'!D23</f>
+        <f>'03_Revenue_Model'!D26</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>'03_Revenue_Model'!E23</f>
+        <f>'03_Revenue_Model'!E26</f>
         <v/>
       </c>
       <c r="F6" s="8">
-        <f>'03_Revenue_Model'!F23</f>
+        <f>'03_Revenue_Model'!F26</f>
         <v/>
       </c>
       <c r="G6" s="8">
-        <f>'03_Revenue_Model'!G23</f>
+        <f>'03_Revenue_Model'!G26</f>
         <v/>
       </c>
       <c r="H6" s="8">
-        <f>'03_Revenue_Model'!H23</f>
+        <f>'03_Revenue_Model'!H26</f>
         <v/>
       </c>
       <c r="I6" s="8">
-        <f>'03_Revenue_Model'!I23</f>
+        <f>'03_Revenue_Model'!I26</f>
         <v/>
       </c>
     </row>
@@ -12260,35 +12260,35 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>'03_Revenue_Model'!B24</f>
+        <f>'03_Revenue_Model'!B27</f>
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>'03_Revenue_Model'!C24</f>
+        <f>'03_Revenue_Model'!C27</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>'03_Revenue_Model'!D24</f>
+        <f>'03_Revenue_Model'!D27</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>'03_Revenue_Model'!E24</f>
+        <f>'03_Revenue_Model'!E27</f>
         <v/>
       </c>
       <c r="F7" s="8">
-        <f>'03_Revenue_Model'!F24</f>
+        <f>'03_Revenue_Model'!F27</f>
         <v/>
       </c>
       <c r="G7" s="8">
-        <f>'03_Revenue_Model'!G24</f>
+        <f>'03_Revenue_Model'!G27</f>
         <v/>
       </c>
       <c r="H7" s="8">
-        <f>'03_Revenue_Model'!H24</f>
+        <f>'03_Revenue_Model'!H27</f>
         <v/>
       </c>
       <c r="I7" s="8">
-        <f>'03_Revenue_Model'!I24</f>
+        <f>'03_Revenue_Model'!I27</f>
         <v/>
       </c>
     </row>
@@ -12299,35 +12299,35 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>'03_Revenue_Model'!B25</f>
+        <f>'03_Revenue_Model'!B28</f>
         <v/>
       </c>
       <c r="C8" s="8">
-        <f>'03_Revenue_Model'!C25</f>
+        <f>'03_Revenue_Model'!C28</f>
         <v/>
       </c>
       <c r="D8" s="8">
-        <f>'03_Revenue_Model'!D25</f>
+        <f>'03_Revenue_Model'!D28</f>
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>'03_Revenue_Model'!E25</f>
+        <f>'03_Revenue_Model'!E28</f>
         <v/>
       </c>
       <c r="F8" s="8">
-        <f>'03_Revenue_Model'!F25</f>
+        <f>'03_Revenue_Model'!F28</f>
         <v/>
       </c>
       <c r="G8" s="8">
-        <f>'03_Revenue_Model'!G25</f>
+        <f>'03_Revenue_Model'!G28</f>
         <v/>
       </c>
       <c r="H8" s="8">
-        <f>'03_Revenue_Model'!H25</f>
+        <f>'03_Revenue_Model'!H28</f>
         <v/>
       </c>
       <c r="I8" s="8">
-        <f>'03_Revenue_Model'!I25</f>
+        <f>'03_Revenue_Model'!I28</f>
         <v/>
       </c>
     </row>
@@ -12338,35 +12338,35 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>'03_Revenue_Model'!B26</f>
+        <f>'03_Revenue_Model'!B29</f>
         <v/>
       </c>
       <c r="C9" s="8">
-        <f>'03_Revenue_Model'!C26</f>
+        <f>'03_Revenue_Model'!C29</f>
         <v/>
       </c>
       <c r="D9" s="8">
-        <f>'03_Revenue_Model'!D26</f>
+        <f>'03_Revenue_Model'!D29</f>
         <v/>
       </c>
       <c r="E9" s="8">
-        <f>'03_Revenue_Model'!E26</f>
+        <f>'03_Revenue_Model'!E29</f>
         <v/>
       </c>
       <c r="F9" s="8">
-        <f>'03_Revenue_Model'!F26</f>
+        <f>'03_Revenue_Model'!F29</f>
         <v/>
       </c>
       <c r="G9" s="8">
-        <f>'03_Revenue_Model'!G26</f>
+        <f>'03_Revenue_Model'!G29</f>
         <v/>
       </c>
       <c r="H9" s="8">
-        <f>'03_Revenue_Model'!H26</f>
+        <f>'03_Revenue_Model'!H29</f>
         <v/>
       </c>
       <c r="I9" s="8">
-        <f>'03_Revenue_Model'!I26</f>
+        <f>'03_Revenue_Model'!I29</f>
         <v/>
       </c>
     </row>
@@ -12811,23 +12811,23 @@
         </is>
       </c>
       <c r="B26" s="23">
-        <f>'03_Revenue_Model'!G12*-0.2</f>
+        <f>'03_Revenue_Model'!G15*-0.2</f>
         <v/>
       </c>
       <c r="C26" s="23">
-        <f>'03_Revenue_Model'!G12*-0.1</f>
+        <f>'03_Revenue_Model'!G15*-0.1</f>
         <v/>
       </c>
       <c r="D26" s="23">
-        <f>'03_Revenue_Model'!G12*0</f>
+        <f>'03_Revenue_Model'!G15*0</f>
         <v/>
       </c>
       <c r="E26" s="23">
-        <f>'03_Revenue_Model'!G12*0.1</f>
+        <f>'03_Revenue_Model'!G15*0.1</f>
         <v/>
       </c>
       <c r="F26" s="23">
-        <f>'03_Revenue_Model'!G12*0.2</f>
+        <f>'03_Revenue_Model'!G15*0.2</f>
         <v/>
       </c>
       <c r="G26" s="7" t="n"/>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="B2" s="49" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Vietcap vận hành mô hình 5 mảng: Môi giới, Cho vay Margin, Tự doanh (FVTPL), IB+Lưu ký, Quản lý quỹ. Mảng đóng góp lớn nhất hiện tại: Cho vay Margin (42.5% DT).</t>
+          <t>Công ty Cổ phần Chứng khoán Vietcap vận hành mô hình 5 mảng: Môi giới, Cho vay Margin, Tự doanh (FVTPL), IB+Lưu ký, Quản lý quỹ. Mảng đóng góp lớn nhất hiện tại: Cho vay Margin (41.7% DT).</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="B4" s="49" t="inlineStr">
         <is>
-          <t>Upside +25.8% so với giá hiện tại theo mô hình P/B (60%) + P/E (40%).</t>
+          <t>Upside +23.1% so với giá hiện tại theo mô hình P/B (60%) + P/E (40%).</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -13138,13 +13138,13 @@
         <v>4980.201525108</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>3662.2</v>
+        <v>3729.3</v>
       </c>
       <c r="H2" s="23" t="n">
-        <v>3217.8</v>
+        <v>3315.2</v>
       </c>
       <c r="I2" s="23" t="n">
-        <v>3449.7</v>
+        <v>3553.9</v>
       </c>
     </row>
     <row r="3">
@@ -13169,13 +13169,13 @@
         <v>1341.954507258</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>1466.5</v>
+        <v>1196</v>
       </c>
       <c r="H3" s="23" t="n">
-        <v>1318.8</v>
+        <v>684.5</v>
       </c>
       <c r="I3" s="23" t="n">
-        <v>1413.9</v>
+        <v>736.3</v>
       </c>
     </row>
     <row r="4">
@@ -13200,13 +13200,13 @@
         <v>1165</v>
       </c>
       <c r="G4" s="23" t="n">
-        <v>1273</v>
+        <v>1038</v>
       </c>
       <c r="H4" s="23" t="n">
-        <v>1145</v>
+        <v>594</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>1227</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5">
@@ -13231,13 +13231,13 @@
         <v>15630</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>16649</v>
+        <v>16461</v>
       </c>
       <c r="H5" s="23" t="n">
-        <v>17564</v>
+        <v>16936</v>
       </c>
       <c r="I5" s="23" t="n">
-        <v>18546</v>
+        <v>17447</v>
       </c>
     </row>
     <row r="6">
@@ -13262,13 +13262,13 @@
         <v>18009.896539949</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>19183.096539949</v>
+        <v>18966.696539949</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>20238.136539949</v>
+        <v>19514.296539949</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>21369.256539949</v>
+        <v>20103.336539949</v>
       </c>
     </row>
     <row r="7">
@@ -13293,13 +13293,13 @@
         <v>7.45</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>7.64</v>
+        <v>6.31</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>6.52</v>
+        <v>3.51</v>
       </c>
       <c r="I7" s="53" t="n">
-        <v>6.62</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="8">
@@ -13324,13 +13324,13 @@
         <v>20.99</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>19.21</v>
+        <v>23.55</v>
       </c>
       <c r="H8" s="34" t="n">
-        <v>21.35</v>
+        <v>41.16</v>
       </c>
       <c r="I8" s="34" t="n">
-        <v>19.93</v>
+        <v>38.26</v>
       </c>
     </row>
     <row r="9">
@@ -13355,13 +13355,13 @@
         <v>1.56</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="H9" s="34" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="I9" s="34" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -13924,15 +13924,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13953,7 +13958,7 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>DT Tự doanh (net)</t>
+          <t>DT Tự doanh (FVTPL+AFS)</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
@@ -13962,6 +13967,31 @@
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>DT QLQ (ước tính)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>LNG Môi giới</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>LNG Margin</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>LNG Tự doanh</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>LNG IB+Lưu ký</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>LNST</t>
         </is>
@@ -13986,6 +14016,21 @@
         <v>17.1</v>
       </c>
       <c r="F2" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>243.9</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>133.9</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K2" s="13" t="n">
         <v>332.3</v>
       </c>
     </row>
@@ -14008,6 +14053,21 @@
         <v>5.9</v>
       </c>
       <c r="F3" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>244.9</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="I3" s="13" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="J3" s="13" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="K3" s="13" t="n">
         <v>198.3</v>
       </c>
     </row>
@@ -14030,6 +14090,21 @@
         <v>7.7</v>
       </c>
       <c r="F4" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="K4" s="13" t="n">
         <v>160.6</v>
       </c>
     </row>
@@ -14052,6 +14127,21 @@
         <v>15.8</v>
       </c>
       <c r="F5" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K5" s="13" t="n">
         <v>131.3</v>
       </c>
     </row>
@@ -14074,6 +14164,21 @@
         <v>5.9</v>
       </c>
       <c r="F6" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>201.3</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="K6" s="13" t="n">
         <v>202.6</v>
       </c>
     </row>
@@ -14096,6 +14201,21 @@
         <v>22.6</v>
       </c>
       <c r="F7" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>76</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K7" s="13" t="n">
         <v>139.6</v>
       </c>
     </row>
@@ -14118,6 +14238,21 @@
         <v>10.8</v>
       </c>
       <c r="F8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="13" t="n">
         <v>150.4</v>
       </c>
     </row>
@@ -14140,6 +14275,21 @@
         <v>29.2</v>
       </c>
       <c r="F9" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="K9" s="13" t="n">
         <v>200.5</v>
       </c>
     </row>
@@ -14162,6 +14312,21 @@
         <v>4.5</v>
       </c>
       <c r="F10" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="K10" s="13" t="n">
         <v>118.6</v>
       </c>
     </row>
@@ -14184,6 +14349,21 @@
         <v>7.1</v>
       </c>
       <c r="F11" s="13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>287.7</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="K11" s="13" t="n">
         <v>205.1</v>
       </c>
     </row>
@@ -14206,6 +14386,21 @@
         <v>6.8</v>
       </c>
       <c r="F12" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="K12" s="13" t="n">
         <v>95.5</v>
       </c>
     </row>
@@ -14228,6 +14423,21 @@
         <v>30.4</v>
       </c>
       <c r="F13" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>304.9</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="K13" s="13" t="n">
         <v>349.8</v>
       </c>
     </row>
@@ -14250,6 +14460,21 @@
         <v>7.2</v>
       </c>
       <c r="F14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K14" s="13" t="n">
         <v>291.9</v>
       </c>
     </row>
@@ -14272,6 +14497,21 @@
         <v>3.9</v>
       </c>
       <c r="F15" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>440</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="K15" s="13" t="n">
         <v>410.3</v>
       </c>
     </row>
@@ -14294,6 +14534,21 @@
         <v>43.9</v>
       </c>
       <c r="F16" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>288.2</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="K16" s="13" t="n">
         <v>329.3</v>
       </c>
     </row>
@@ -14316,6 +14571,21 @@
         <v>240.1</v>
       </c>
       <c r="F17" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>169.3</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="K17" s="13" t="n">
         <v>467.3</v>
       </c>
     </row>
@@ -14332,12 +14602,27 @@
         <v>195.6</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>141.1</v>
+        <v>145.3</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>10</v>
       </c>
       <c r="F18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K18" s="13" t="n">
         <v>417.2</v>
       </c>
     </row>
@@ -14354,12 +14639,27 @@
         <v>181</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>85.90000000000001</v>
+        <v>175.9</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>34</v>
       </c>
       <c r="F19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>170.8</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K19" s="13" t="n">
         <v>300.7</v>
       </c>
     </row>
@@ -14382,6 +14682,21 @@
         <v>4.9</v>
       </c>
       <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="K20" s="13" t="n">
         <v>122.7</v>
       </c>
     </row>
@@ -14398,12 +14713,27 @@
         <v>162.4</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>-31.3</v>
+        <v>-18</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>14.3</v>
       </c>
       <c r="F21" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>-24.2</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K21" s="13" t="n">
         <v>28.4</v>
       </c>
     </row>
@@ -14420,12 +14750,27 @@
         <v>155.4</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>59.7</v>
+        <v>102.5</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>22.2</v>
       </c>
       <c r="F22" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>-19.6</v>
+      </c>
+      <c r="K22" s="13" t="n">
         <v>73.09999999999999</v>
       </c>
     </row>
@@ -14442,12 +14787,27 @@
         <v>169.4</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>65.09999999999999</v>
+        <v>125.6</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>6.4</v>
       </c>
       <c r="F23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="K23" s="13" t="n">
         <v>116.9</v>
       </c>
     </row>
@@ -14464,12 +14824,27 @@
         <v>176.9</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>129.6</v>
+        <v>186.4</v>
       </c>
       <c r="E24" s="13" t="n">
         <v>6.8</v>
       </c>
       <c r="F24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="K24" s="13" t="n">
         <v>179</v>
       </c>
     </row>
@@ -14486,12 +14861,27 @@
         <v>187.2</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>192.3</v>
+        <v>206.6</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>16</v>
       </c>
       <c r="F25" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>190.7</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="K25" s="13" t="n">
         <v>123</v>
       </c>
     </row>
@@ -14508,12 +14898,27 @@
         <v>180.2</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>184.6</v>
+        <v>264</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>6.2</v>
       </c>
       <c r="F26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>250.3</v>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="K26" s="13" t="n">
         <v>197.8</v>
       </c>
     </row>
@@ -14530,12 +14935,27 @@
         <v>234.5</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>249.2</v>
+        <v>276.4</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>20.1</v>
       </c>
       <c r="F27" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>265.6</v>
+      </c>
+      <c r="J27" s="13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K27" s="13" t="n">
         <v>279.2</v>
       </c>
     </row>
@@ -14552,12 +14972,27 @@
         <v>206.4</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>282.9</v>
+        <v>312.4</v>
       </c>
       <c r="E28" s="13" t="n">
         <v>15.2</v>
       </c>
       <c r="F28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I28" s="13" t="n">
+        <v>298.3</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="K28" s="13" t="n">
         <v>215.4</v>
       </c>
     </row>
@@ -14574,12 +15009,27 @@
         <v>251.9</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>70.2</v>
+        <v>159.2</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>23.4</v>
       </c>
       <c r="F29" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K29" s="13" t="n">
         <v>218.4</v>
       </c>
     </row>
@@ -14596,12 +15046,27 @@
         <v>257</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>200</v>
+        <v>254.4</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>23.9</v>
       </c>
       <c r="F30" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>240.6</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K30" s="13" t="n">
         <v>294.9</v>
       </c>
     </row>
@@ -14618,12 +15083,27 @@
         <v>257.7</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>-12.3</v>
+        <v>68.8</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>7.8</v>
       </c>
       <c r="F31" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="K31" s="13" t="n">
         <v>183.9</v>
       </c>
     </row>
@@ -14640,12 +15120,27 @@
         <v>313.8</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>261.2</v>
+        <v>320.3</v>
       </c>
       <c r="E32" s="13" t="n">
         <v>13</v>
       </c>
       <c r="F32" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>136</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="I32" s="13" t="n">
+        <v>309.7</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="K32" s="13" t="n">
         <v>420.3</v>
       </c>
     </row>
@@ -14662,12 +15157,27 @@
         <v>376.3</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>371.1</v>
+        <v>453.6</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>51.5</v>
       </c>
       <c r="F33" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K33" s="13" t="n">
         <v>442.9</v>
       </c>
     </row>
@@ -14684,12 +15194,27 @@
         <v>414.5</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>61.4</v>
+        <v>188.1</v>
       </c>
       <c r="E34" s="13" t="n">
         <v>15.8</v>
       </c>
       <c r="F34" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>176.4</v>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="I34" s="13" t="n">
+        <v>178.1</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="K34" s="13" t="n">
         <v>340.7</v>
       </c>
     </row>
@@ -15697,37 +16222,37 @@
         </is>
       </c>
       <c r="B6" s="57" t="n">
-        <v>66.7</v>
+        <v>2908.4</v>
       </c>
       <c r="C6" s="57" t="n">
-        <v>122.1</v>
+        <v>5873</v>
       </c>
       <c r="D6" s="57" t="n">
-        <v>412.6</v>
+        <v>7247</v>
       </c>
       <c r="E6" s="57" t="n">
-        <v>753.8</v>
+        <v>7726.6</v>
       </c>
       <c r="F6" s="57" t="n">
-        <v>2.1</v>
+        <v>5664.1</v>
       </c>
       <c r="G6" s="57" t="n">
-        <v>197.3</v>
+        <v>7216.5</v>
       </c>
       <c r="H6" s="57" t="n">
-        <v>823.8</v>
+        <v>7501.7</v>
       </c>
       <c r="I6" s="57" t="n">
-        <v>32.2</v>
+        <v>6680.2</v>
       </c>
       <c r="J6" s="57" t="n">
-        <v>156.4</v>
+        <v>9039.799999999999</v>
       </c>
       <c r="K6" s="57" t="n">
-        <v>45</v>
+        <v>10593.2</v>
       </c>
       <c r="L6" s="57" t="n">
-        <v>549.2</v>
+        <v>11258.9</v>
       </c>
     </row>
     <row r="7">
@@ -15737,37 +16262,37 @@
         </is>
       </c>
       <c r="B7" s="57" t="n">
-        <v>0</v>
+        <v>892.3</v>
       </c>
       <c r="C7" s="57" t="n">
-        <v>0</v>
+        <v>853</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>0</v>
+        <v>853</v>
       </c>
       <c r="E7" s="57" t="n">
-        <v>0</v>
+        <v>851.4</v>
       </c>
       <c r="F7" s="57" t="n">
-        <v>0</v>
+        <v>851.4</v>
       </c>
       <c r="G7" s="57" t="n">
-        <v>0</v>
+        <v>846.1</v>
       </c>
       <c r="H7" s="57" t="n">
-        <v>0</v>
+        <v>846.1</v>
       </c>
       <c r="I7" s="57" t="n">
-        <v>0</v>
+        <v>846.1</v>
       </c>
       <c r="J7" s="57" t="n">
-        <v>0</v>
+        <v>1114.6</v>
       </c>
       <c r="K7" s="57" t="n">
-        <v>0</v>
+        <v>1080.1</v>
       </c>
       <c r="L7" s="57" t="n">
-        <v>0</v>
+        <v>1075.3</v>
       </c>
     </row>
     <row r="8">
@@ -15786,28 +16311,28 @@
         <v>0</v>
       </c>
       <c r="E8" s="57" t="n">
-        <v>40.6</v>
+        <v>729.8</v>
       </c>
       <c r="F8" s="57" t="n">
         <v>452.5</v>
       </c>
       <c r="G8" s="57" t="n">
-        <v>628.6</v>
+        <v>1172</v>
       </c>
       <c r="H8" s="57" t="n">
         <v>271.9</v>
       </c>
       <c r="I8" s="57" t="n">
-        <v>713.5</v>
+        <v>1002.3</v>
       </c>
       <c r="J8" s="57" t="n">
-        <v>443</v>
+        <v>1901.5</v>
       </c>
       <c r="K8" s="57" t="n">
-        <v>2135.2</v>
+        <v>3814.7</v>
       </c>
       <c r="L8" s="57" t="n">
-        <v>1316.9</v>
+        <v>2620.6</v>
       </c>
     </row>
     <row r="9">
@@ -16017,35 +16542,37 @@
         </is>
       </c>
       <c r="B16" s="57" t="n">
-        <v>-1.6</v>
+        <v>1098.5</v>
       </c>
       <c r="C16" s="57" t="n">
-        <v>-2.9</v>
+        <v>1819.1</v>
       </c>
       <c r="D16" s="57" t="n">
-        <v>7.5</v>
+        <v>2590</v>
       </c>
       <c r="E16" s="57" t="n">
-        <v>-9</v>
+        <v>2859.4</v>
       </c>
       <c r="F16" s="57" t="n">
-        <v>0.1</v>
+        <v>2700.2</v>
       </c>
       <c r="G16" s="57" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="H16" s="57" t="n"/>
+        <v>-7.8</v>
+      </c>
+      <c r="H16" s="57" t="n">
+        <v>2178.5</v>
+      </c>
       <c r="I16" s="57" t="n">
-        <v>-0.8</v>
+        <v>1673.1</v>
       </c>
       <c r="J16" s="57" t="n">
-        <v>-4.2</v>
+        <v>1463.8</v>
       </c>
       <c r="K16" s="57" t="n">
         <v>-0.4</v>
       </c>
       <c r="L16" s="57" t="n">
-        <v>9.5</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="17">
@@ -16055,37 +16582,37 @@
         </is>
       </c>
       <c r="B17" s="57" t="n">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="C17" s="57" t="n">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="D17" s="57" t="n">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="E17" s="57" t="n">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="F17" s="57" t="n">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="G17" s="57" t="n">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="H17" s="57" t="n">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="I17" s="57" t="n">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="J17" s="57" t="n">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="K17" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="57" t="n">
-        <v>0</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="18">
@@ -16104,26 +16631,28 @@
         <v>0</v>
       </c>
       <c r="E18" s="57" t="n">
-        <v>0</v>
+        <v>150.6</v>
       </c>
       <c r="F18" s="57" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="57" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="H18" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="57" t="n"/>
       <c r="I18" s="57" t="n">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="J18" s="57" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K18" s="57" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="57" t="n">
-        <v>0</v>
+        <v>208.2</v>
       </c>
     </row>
     <row r="19">
@@ -16493,7 +17022,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Cache lần chạy trước (2026-07-11 19:01)</t>
+          <t>Cache lần chạy trước (2026-07-11 21:58)</t>
         </is>
       </c>
     </row>
@@ -16632,7 +17161,7 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>32133</v>
+        <v>31770</v>
       </c>
     </row>
     <row r="11">
@@ -16642,7 +17171,7 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>18344</v>
+        <v>14958</v>
       </c>
     </row>
     <row r="12">
@@ -16675,7 +17204,7 @@
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>30754</v>
+        <v>30089</v>
       </c>
     </row>
     <row r="16">
@@ -16685,7 +17214,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.258</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="17">
@@ -16714,7 +17243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -17020,23 +17549,23 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>'03_Revenue_Model'!B12/(B11*B12*B13/10000)</f>
+        <f>'03_Revenue_Model'!B15/(B11*B12*B13/10000)</f>
         <v/>
       </c>
       <c r="C14" s="8">
-        <f>'03_Revenue_Model'!C12/(C11*C12*C13/10000)</f>
+        <f>'03_Revenue_Model'!C15/(C11*C12*C13/10000)</f>
         <v/>
       </c>
       <c r="D14" s="8">
-        <f>'03_Revenue_Model'!D12/(D11*D12*D13/10000)</f>
+        <f>'03_Revenue_Model'!D15/(D11*D12*D13/10000)</f>
         <v/>
       </c>
       <c r="E14" s="8">
-        <f>'03_Revenue_Model'!E12/(E11*E12*E13/10000)</f>
+        <f>'03_Revenue_Model'!E15/(E11*E12*E13/10000)</f>
         <v/>
       </c>
       <c r="F14" s="8">
-        <f>'03_Revenue_Model'!F12/(F11*F12*F13/10000)</f>
+        <f>'03_Revenue_Model'!F15/(F11*F12*F13/10000)</f>
         <v/>
       </c>
       <c r="G14" s="21">
@@ -17071,23 +17600,23 @@
         </is>
       </c>
       <c r="B16" s="8">
-        <f>'03_Revenue_Model'!B13/'03_Revenue_Model'!B4</f>
+        <f>'03_Revenue_Model'!B16/'03_Revenue_Model'!B4</f>
         <v/>
       </c>
       <c r="C16" s="8">
-        <f>'03_Revenue_Model'!C13/'03_Revenue_Model'!C4</f>
+        <f>'03_Revenue_Model'!C16/'03_Revenue_Model'!C4</f>
         <v/>
       </c>
       <c r="D16" s="8">
-        <f>'03_Revenue_Model'!D13/'03_Revenue_Model'!D4</f>
+        <f>'03_Revenue_Model'!D16/'03_Revenue_Model'!D4</f>
         <v/>
       </c>
       <c r="E16" s="8">
-        <f>'03_Revenue_Model'!E13/'03_Revenue_Model'!E4</f>
+        <f>'03_Revenue_Model'!E16/'03_Revenue_Model'!E4</f>
         <v/>
       </c>
       <c r="F16" s="8">
-        <f>'03_Revenue_Model'!F13/'03_Revenue_Model'!F4</f>
+        <f>'03_Revenue_Model'!F16/'03_Revenue_Model'!F4</f>
         <v/>
       </c>
       <c r="G16" s="21">
@@ -17153,13 +17682,13 @@
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="21" t="n">
-        <v>0.2007</v>
+        <v>0.0327</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>0.2007</v>
+        <v>0.0327</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>0.2007</v>
+        <v>0.0327</v>
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
@@ -17179,13 +17708,13 @@
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="21" t="n">
-        <v>0.5162</v>
+        <v>0.1676</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>0.5162</v>
+        <v>0.1676</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>0.5162</v>
+        <v>0.1676</v>
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
@@ -17205,13 +17734,13 @@
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="21" t="n">
-        <v>0.2832</v>
+        <v>0.7997</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>0.2832</v>
+        <v>0.7997</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>0.2832</v>
+        <v>0.7997</v>
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
@@ -17330,23 +17859,23 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>'03_Revenue_Model'!B14/'03_Revenue_Model'!B7</f>
+        <f>'03_Revenue_Model'!B17/'03_Revenue_Model'!B7</f>
         <v/>
       </c>
       <c r="C26" s="8">
-        <f>'03_Revenue_Model'!C14/'03_Revenue_Model'!C7</f>
+        <f>'03_Revenue_Model'!C17/'03_Revenue_Model'!C7</f>
         <v/>
       </c>
       <c r="D26" s="8">
-        <f>'03_Revenue_Model'!D14/'03_Revenue_Model'!D7</f>
+        <f>'03_Revenue_Model'!D17/'03_Revenue_Model'!D7</f>
         <v/>
       </c>
       <c r="E26" s="8">
-        <f>'03_Revenue_Model'!E14/'03_Revenue_Model'!E7</f>
+        <f>'03_Revenue_Model'!E17/'03_Revenue_Model'!E7</f>
         <v/>
       </c>
       <c r="F26" s="8">
-        <f>'03_Revenue_Model'!F14/'03_Revenue_Model'!F7</f>
+        <f>'03_Revenue_Model'!F17/'03_Revenue_Model'!F7</f>
         <v/>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -17524,83 +18053,266 @@
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>── CHI PHÍ &amp; THUẾ ──</t>
+          <t>── CHI PHÍ THEO MẢNG (giá vốn — dùng cho Lợi nhuận gộp bottom-up theo mảng) ──</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Chi phí hoạt động / DT hoạt động (%)</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="21" t="n">
-        <v>0.4724</v>
-      </c>
-      <c r="H36" s="21" t="n">
-        <v>0.4724</v>
-      </c>
-      <c r="I36" s="21" t="n">
-        <v>0.4724</v>
+          <t>Tỷ lệ Chi phí Môi giới / DT Môi giới (%)</t>
+        </is>
+      </c>
+      <c r="B36" s="8">
+        <f>'03_Revenue_Model'!B31/'03_Revenue_Model'!B15</f>
+        <v/>
+      </c>
+      <c r="C36" s="8">
+        <f>'03_Revenue_Model'!C31/'03_Revenue_Model'!C15</f>
+        <v/>
+      </c>
+      <c r="D36" s="8">
+        <f>'03_Revenue_Model'!D31/'03_Revenue_Model'!D15</f>
+        <v/>
+      </c>
+      <c r="E36" s="8">
+        <f>'03_Revenue_Model'!E31/'03_Revenue_Model'!E15</f>
+        <v/>
+      </c>
+      <c r="F36" s="8">
+        <f>'03_Revenue_Model'!F31/'03_Revenue_Model'!F15</f>
+        <v/>
+      </c>
+      <c r="G36" s="21">
+        <f>AVERAGE(E36:F36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="21">
+        <f>AVERAGE(E36:F36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="21">
+        <f>AVERAGE(E36:F36)</f>
+        <v/>
       </c>
       <c r="J36" s="20" t="inlineStr">
         <is>
-          <t>TB 2 năm gần nhất (chi phí môi giới, lưu ký, tự doanh...) — số derive từ lịch sử, có thể điều chỉnh nếu dự kiến thay đổi cơ cấu chi phí</t>
+          <t>Công thức: Chi phí môi giới thực tế / DT môi giới ('03_Revenue_Model') — công thức sống; Dự phóng = TB 2 năm gần nhất (thay cho tỷ lệ chi phí gộp chung toàn công ty)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>CP Quản lý CTCK / DT hoạt động (%)</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="21" t="n">
-        <v>0.0341</v>
-      </c>
-      <c r="H37" s="21" t="n">
-        <v>0.0341</v>
-      </c>
-      <c r="I37" s="21" t="n">
-        <v>0.0341</v>
+          <t>Chi phí lãi vay / Tổng dư nợ vay bình quân (%/năm)</t>
+        </is>
+      </c>
+      <c r="B37" s="8">
+        <f>'03_Revenue_Model'!B32/'03_Revenue_Model'!B10</f>
+        <v/>
+      </c>
+      <c r="C37" s="8">
+        <f>'03_Revenue_Model'!C32/'03_Revenue_Model'!C10</f>
+        <v/>
+      </c>
+      <c r="D37" s="8">
+        <f>'03_Revenue_Model'!D32/'03_Revenue_Model'!D10</f>
+        <v/>
+      </c>
+      <c r="E37" s="8">
+        <f>'03_Revenue_Model'!E32/'03_Revenue_Model'!E10</f>
+        <v/>
+      </c>
+      <c r="F37" s="8">
+        <f>'03_Revenue_Model'!F32/'03_Revenue_Model'!F10</f>
+        <v/>
+      </c>
+      <c r="G37" s="21">
+        <f>AVERAGE(E37:F37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="21">
+        <f>AVERAGE(E37:F37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="21">
+        <f>AVERAGE(E37:F37)</f>
+        <v/>
       </c>
       <c r="J37" s="20" t="inlineStr">
         <is>
-          <t>TB 2 năm gần nhất — số derive từ lịch sử, điều chỉnh nếu công ty có kế hoạch mở rộng/thu hẹp bộ máy</t>
+          <t>Công thức: Chi phí lãi vay toàn công ty / Dư nợ vay bình quân ('03_Revenue_Model') — công thức sống; Dự phóng = TB 2 năm gần nhất. Giá vốn của mảng Margin — CTCK không tách bạch chi phí vốn theo mảng vay margin/tự doanh trong BCTC công khai, dùng chi phí lãi vay TOÀN CÔNG TY (theo yêu cầu)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
+          <t>Tỷ lệ Chi phí hoạt động Tự doanh / Danh mục bình quân (%/năm)</t>
+        </is>
+      </c>
+      <c r="B38" s="8">
+        <f>'03_Revenue_Model'!B33/'03_Revenue_Model'!B7</f>
+        <v/>
+      </c>
+      <c r="C38" s="8">
+        <f>'03_Revenue_Model'!C33/'03_Revenue_Model'!C7</f>
+        <v/>
+      </c>
+      <c r="D38" s="8">
+        <f>'03_Revenue_Model'!D33/'03_Revenue_Model'!D7</f>
+        <v/>
+      </c>
+      <c r="E38" s="8">
+        <f>'03_Revenue_Model'!E33/'03_Revenue_Model'!E7</f>
+        <v/>
+      </c>
+      <c r="F38" s="8">
+        <f>'03_Revenue_Model'!F33/'03_Revenue_Model'!F7</f>
+        <v/>
+      </c>
+      <c r="G38" s="21">
+        <f>AVERAGE(E38:F38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="21">
+        <f>AVERAGE(E38:F38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="21">
+        <f>AVERAGE(E38:F38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="20" t="inlineStr">
+        <is>
+          <t>Công thức: Chi phí hoạt động tự doanh / Danh mục Tự doanh bình quân ('03_Revenue_Model') — công thức sống; Dự phóng = TB 2 năm gần nhất</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Tỷ lệ Chi phí IB+Lưu ký / DT IB+Lưu ký (%)</t>
+        </is>
+      </c>
+      <c r="B39" s="8">
+        <f>'03_Revenue_Model'!B34/'03_Revenue_Model'!B20</f>
+        <v/>
+      </c>
+      <c r="C39" s="8">
+        <f>'03_Revenue_Model'!C34/'03_Revenue_Model'!C20</f>
+        <v/>
+      </c>
+      <c r="D39" s="8">
+        <f>'03_Revenue_Model'!D34/'03_Revenue_Model'!D20</f>
+        <v/>
+      </c>
+      <c r="E39" s="8">
+        <f>'03_Revenue_Model'!E34/'03_Revenue_Model'!E20</f>
+        <v/>
+      </c>
+      <c r="F39" s="8">
+        <f>'03_Revenue_Model'!F34/'03_Revenue_Model'!F20</f>
+        <v/>
+      </c>
+      <c r="G39" s="21">
+        <f>AVERAGE(E39:F39)</f>
+        <v/>
+      </c>
+      <c r="H39" s="21">
+        <f>AVERAGE(E39:F39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="21">
+        <f>AVERAGE(E39:F39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="20" t="inlineStr">
+        <is>
+          <t>Công thức: (Chi phí bảo lãnh+tư vấn+lưu ký) / DT IB+Lưu ký ('03_Revenue_Model') — công thức sống; Dự phóng = TB 2 năm gần nhất</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>── CHI PHÍ &amp; THUẾ (tổng công ty) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Chi phí hoạt động / DT hoạt động (%, THAM CHIẾU — không dùng để dự phóng)</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="21" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="H41" s="21" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="I41" s="21" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="J41" s="20" t="inlineStr">
+        <is>
+          <t>⚠ CHỈ ĐỂ THAM CHIẾU/ĐỐI CHIẾU — dự phóng LỢI NHUẬN GỘP chính thức nay dùng tổng chi phí bottom-up 4 dòng trên (theo mảng), KHÔNG dùng tỷ lệ gộp chung này nữa (xem 03_Revenue_Model mục CHI PHÍ/LỢI NHUẬN GỘP THEO MẢNG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>CP Quản lý CTCK / DT hoạt động (%)</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="21" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="H42" s="21" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="I42" s="21" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="J42" s="20" t="inlineStr">
+        <is>
+          <t>TB 2 năm gần nhất — số derive từ lịch sử, điều chỉnh nếu công ty có kế hoạch mở rộng/thu hẹp bộ máy</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
           <t>Thuế suất TNDN hiệu dụng (%)</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="21" t="n">
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="21" t="n">
         <v>0.1695</v>
       </c>
-      <c r="H38" s="21" t="n">
+      <c r="H43" s="21" t="n">
         <v>0.1695</v>
       </c>
-      <c r="I38" s="21" t="n">
+      <c r="I43" s="21" t="n">
         <v>0.1695</v>
       </c>
-      <c r="J38" s="20" t="inlineStr">
+      <c r="J43" s="20" t="inlineStr">
         <is>
           <t>TB thuế suất hiệu dụng lịch sử (giới hạn 15%-22%) — điều chỉnh nếu công ty có ưu đãi thuế đặc biệt</t>
         </is>
@@ -17617,7 +18329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -17827,527 +18539,945 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>AUM Quản lý quỹ (cuối kỳ)</t>
-        </is>
+          <t>Tổng vay &amp; nợ thuê tài chính (cuối kỳ)</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>6362.7</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>6326.2</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>8979.299999999999</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>12573.9</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>16064.5</v>
       </c>
       <c r="G9" s="13">
-        <f>'02_Assumptions'!G32</f>
+        <f>F9*(1+'02_Assumptions'!G17)</f>
         <v/>
       </c>
       <c r="H9" s="13">
-        <f>G9*(1+'02_Assumptions'!H34)</f>
+        <f>G9*(1+'02_Assumptions'!H17)</f>
         <v/>
       </c>
       <c r="I9" s="13">
-        <f>H9*(1+'02_Assumptions'!I34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>── DOANH THU THEO MẢNG (tỷ VND) ──</t>
-        </is>
+        <f>H9*(1+'02_Assumptions'!I17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tổng vay &amp; nợ thuê bình quân</t>
+        </is>
+      </c>
+      <c r="B10" s="13">
+        <f>AVERAGE(B9:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="13">
+        <f>AVERAGE(B9:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="13">
+        <f>AVERAGE(C9:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="13">
+        <f>AVERAGE(D9:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="13">
+        <f>AVERAGE(E9:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="13">
+        <f>AVERAGE(F9:G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="13">
+        <f>AVERAGE(G9:H9)</f>
+        <v/>
+      </c>
+      <c r="I10" s="13">
+        <f>AVERAGE(H9:I9)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
+          <t>AUM Quản lý quỹ (cuối kỳ)</t>
+        </is>
+      </c>
+      <c r="G12" s="13">
+        <f>'02_Assumptions'!G32</f>
+        <v/>
+      </c>
+      <c r="H12" s="13">
+        <f>G12*(1+'02_Assumptions'!H34)</f>
+        <v/>
+      </c>
+      <c r="I12" s="13">
+        <f>H12*(1+'02_Assumptions'!I34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>── DOANH THU THEO MẢNG (tỷ VND) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
           <t>(1) DT Môi giới</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B15" s="13" t="n">
         <v>857.3</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C15" s="13" t="n">
         <v>1011.2</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D15" s="13" t="n">
         <v>535.4</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E15" s="13" t="n">
         <v>729.6</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F15" s="13" t="n">
         <v>1000.2</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G15" s="13">
         <f>'02_Assumptions'!G11*'02_Assumptions'!G12*'02_Assumptions'!G14*'02_Assumptions'!G13/10000</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H15" s="13">
         <f>'02_Assumptions'!H11*'02_Assumptions'!H12*'02_Assumptions'!H14*'02_Assumptions'!H13/10000</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I15" s="13">
         <f>'02_Assumptions'!I11*'02_Assumptions'!I12*'02_Assumptions'!I14*'02_Assumptions'!I13/10000</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>(2) DT Cho vay Margin</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B16" s="13" t="n">
         <v>576.9</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C16" s="13" t="n">
         <v>708.2</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D16" s="13" t="n">
         <v>689</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E16" s="13" t="n">
         <v>872.9</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F16" s="13" t="n">
         <v>1204.8</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G16" s="13">
         <f>G4*'02_Assumptions'!G16</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H16" s="13">
         <f>H4*'02_Assumptions'!H16</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I16" s="13">
         <f>I4*'02_Assumptions'!I16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>(3) DT Tự doanh (FVTPL)</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>1214.2</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>301.3</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>446.7</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>786.9</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>820</v>
-      </c>
-      <c r="G14" s="13">
-        <f>G7*('02_Assumptions'!G19*'02_Assumptions'!G22+'02_Assumptions'!G20*'02_Assumptions'!G23+'02_Assumptions'!G21*'02_Assumptions'!G24)</f>
-        <v/>
-      </c>
-      <c r="H14" s="13">
-        <f>H7*('02_Assumptions'!H19*'02_Assumptions'!H22+'02_Assumptions'!H20*'02_Assumptions'!H23+'02_Assumptions'!H21*'02_Assumptions'!H24)</f>
-        <v/>
-      </c>
-      <c r="I14" s="13">
-        <f>I7*('02_Assumptions'!I19*'02_Assumptions'!I22+'02_Assumptions'!I20*'02_Assumptions'!I23+'02_Assumptions'!I21*'02_Assumptions'!I24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  IB (bảo lãnh/tư vấn)</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>285.6</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="G15" s="13">
-        <f>'02_Assumptions'!G28*'02_Assumptions'!G29</f>
-        <v/>
-      </c>
-      <c r="H15" s="13">
-        <f>'02_Assumptions'!H28*'02_Assumptions'!H29</f>
-        <v/>
-      </c>
-      <c r="I15" s="13">
-        <f>'02_Assumptions'!I28*'02_Assumptions'!I29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Lưu ký</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="G16" s="13">
-        <f>F16*(1+'02_Assumptions'!G30)</f>
-        <v/>
-      </c>
-      <c r="H16" s="13">
-        <f>G16*(1+'02_Assumptions'!H30)</f>
-        <v/>
-      </c>
-      <c r="I16" s="13">
-        <f>H16*(1+'02_Assumptions'!I30)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>(4) DT IB + Lưu ký</t>
-        </is>
-      </c>
-      <c r="B17" s="13">
-        <f>B15+B16</f>
-        <v/>
-      </c>
-      <c r="C17" s="13">
-        <f>C15+C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="13">
-        <f>D15+D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="13">
-        <f>E15+E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="13">
-        <f>F15+F16</f>
-        <v/>
+          <t>(3) DT Tự doanh (FVTPL)</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>1308.7</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>408.7</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>621.1</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>1011.9</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>1097.1</v>
       </c>
       <c r="G17" s="13">
-        <f>G15+G16</f>
+        <f>G7*('02_Assumptions'!G19*'02_Assumptions'!G22+'02_Assumptions'!G20*'02_Assumptions'!G23+'02_Assumptions'!G21*'02_Assumptions'!G24)</f>
         <v/>
       </c>
       <c r="H17" s="13">
-        <f>H15+H16</f>
+        <f>H7*('02_Assumptions'!H19*'02_Assumptions'!H22+'02_Assumptions'!H20*'02_Assumptions'!H23+'02_Assumptions'!H21*'02_Assumptions'!H24)</f>
         <v/>
       </c>
       <c r="I17" s="13">
-        <f>I15+I16</f>
+        <f>I7*('02_Assumptions'!I19*'02_Assumptions'!I22+'02_Assumptions'!I20*'02_Assumptions'!I23+'02_Assumptions'!I21*'02_Assumptions'!I24)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>(5) DT Quản lý quỹ (QLQ)</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  IB (bảo lãnh/tư vấn)</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>6.2</v>
+        <v>285.6</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>0.1</v>
+        <v>52.1</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>0.5</v>
+        <v>39.3</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>0.5</v>
+        <v>50.6</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G18" s="13">
-        <f>G9*'02_Assumptions'!G33</f>
+        <f>'02_Assumptions'!G28*'02_Assumptions'!G29</f>
         <v/>
       </c>
       <c r="H18" s="13">
-        <f>H9*'02_Assumptions'!H33</f>
+        <f>'02_Assumptions'!H28*'02_Assumptions'!H29</f>
         <v/>
       </c>
       <c r="I18" s="13">
-        <f>I9*'02_Assumptions'!I33</f>
+        <f>'02_Assumptions'!I28*'02_Assumptions'!I29</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Lưu ký</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G19" s="13">
+        <f>F19*(1+'02_Assumptions'!G30)</f>
+        <v/>
+      </c>
+      <c r="H19" s="13">
+        <f>G19*(1+'02_Assumptions'!H30)</f>
+        <v/>
+      </c>
+      <c r="I19" s="13">
+        <f>H19*(1+'02_Assumptions'!I30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>(4) DT IB + Lưu ký</t>
+        </is>
+      </c>
+      <c r="B20" s="13">
+        <f>B18+B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="13">
+        <f>C18+C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="13">
+        <f>D18+D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="13">
+        <f>E18+E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="13">
+        <f>F18+F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="13">
+        <f>G18+G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="13">
+        <f>H18+H19</f>
+        <v/>
+      </c>
+      <c r="I20" s="13">
+        <f>I18+I19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>(5) DT Quản lý quỹ (QLQ)</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G21" s="13">
+        <f>G12*'02_Assumptions'!G33</f>
+        <v/>
+      </c>
+      <c r="H21" s="13">
+        <f>H12*'02_Assumptions'!H33</f>
+        <v/>
+      </c>
+      <c r="I21" s="13">
+        <f>I12*'02_Assumptions'!I33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Điều chỉnh theo KQKD thực tế đã công bố</t>
         </is>
       </c>
-      <c r="G19" s="13">
+      <c r="G22" s="13">
         <f>'04b_Dien_Bien_Quy'!B12</f>
         <v/>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>TỔNG DOANH THU HOẠT ĐỘNG</t>
         </is>
       </c>
-      <c r="B20" s="29">
-        <f>B12+B13+B14+B17+B18+B19</f>
-        <v/>
-      </c>
-      <c r="C20" s="29">
-        <f>C12+C13+C14+C17+C18+C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="29">
-        <f>D12+D13+D14+D17+D18+D19</f>
-        <v/>
-      </c>
-      <c r="E20" s="29">
-        <f>E12+E13+E14+E17+E18+E19</f>
-        <v/>
-      </c>
-      <c r="F20" s="29">
-        <f>F12+F13+F14+F17+F18+F19</f>
-        <v/>
-      </c>
-      <c r="G20" s="29">
-        <f>G12+G13+G14+G17+G18+G19</f>
-        <v/>
-      </c>
-      <c r="H20" s="29">
-        <f>H12+H13+H14+H17+H18+H19</f>
-        <v/>
-      </c>
-      <c r="I20" s="29">
-        <f>I12+I13+I14+I17+I18+I19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="B23" s="29">
+        <f>B15+B16+B17+B20+B21+B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="29">
+        <f>C15+C16+C17+C20+C21+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>D15+D16+D17+D20+D21+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="29">
+        <f>E15+E16+E17+E20+E21+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f>F15+F16+F17+F20+F21+F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f>G15+G16+G17+G20+G21+G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="29">
+        <f>H15+H16+H17+H20+H21+H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="29">
+        <f>I15+I16+I17+I20+I21+I22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>── TỶ TRỌNG ĐÓNG GÓP THEO MẢNG (%) ──</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  % Môi giới / Tổng DT</t>
-        </is>
-      </c>
-      <c r="B22" s="5">
-        <f>B12/B20</f>
-        <v/>
-      </c>
-      <c r="C22" s="5">
-        <f>C12/C20</f>
-        <v/>
-      </c>
-      <c r="D22" s="5">
-        <f>D12/D20</f>
-        <v/>
-      </c>
-      <c r="E22" s="5">
-        <f>E12/E20</f>
-        <v/>
-      </c>
-      <c r="F22" s="5">
-        <f>F12/F20</f>
-        <v/>
-      </c>
-      <c r="G22" s="5">
-        <f>G12/G20</f>
-        <v/>
-      </c>
-      <c r="H22" s="5">
-        <f>H12/H20</f>
-        <v/>
-      </c>
-      <c r="I22" s="5">
-        <f>I12/I20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  % Cho vay Margin / Tổng DT</t>
-        </is>
-      </c>
-      <c r="B23" s="5">
-        <f>B13/B20</f>
-        <v/>
-      </c>
-      <c r="C23" s="5">
-        <f>C13/C20</f>
-        <v/>
-      </c>
-      <c r="D23" s="5">
-        <f>D13/D20</f>
-        <v/>
-      </c>
-      <c r="E23" s="5">
-        <f>E13/E20</f>
-        <v/>
-      </c>
-      <c r="F23" s="5">
-        <f>F13/F20</f>
-        <v/>
-      </c>
-      <c r="G23" s="5">
-        <f>G13/G20</f>
-        <v/>
-      </c>
-      <c r="H23" s="5">
-        <f>H13/H20</f>
-        <v/>
-      </c>
-      <c r="I23" s="5">
-        <f>I13/I20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  % Tự doanh (FVTPL) / Tổng DT</t>
-        </is>
-      </c>
-      <c r="B24" s="5">
-        <f>B14/B20</f>
-        <v/>
-      </c>
-      <c r="C24" s="5">
-        <f>C14/C20</f>
-        <v/>
-      </c>
-      <c r="D24" s="5">
-        <f>D14/D20</f>
-        <v/>
-      </c>
-      <c r="E24" s="5">
-        <f>E14/E20</f>
-        <v/>
-      </c>
-      <c r="F24" s="5">
-        <f>F14/F20</f>
-        <v/>
-      </c>
-      <c r="G24" s="5">
-        <f>G14/G20</f>
-        <v/>
-      </c>
-      <c r="H24" s="5">
-        <f>H14/H20</f>
-        <v/>
-      </c>
-      <c r="I24" s="5">
-        <f>I14/I20</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  % IB + Lưu ký / Tổng DT</t>
+          <t xml:space="preserve">  % Môi giới / Tổng DT</t>
         </is>
       </c>
       <c r="B25" s="5">
-        <f>B17/B20</f>
+        <f>B15/B23</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>C17/C20</f>
+        <f>C15/C23</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>D17/D20</f>
+        <f>D15/D23</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>E17/E20</f>
+        <f>E15/E23</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>F17/F20</f>
+        <f>F15/F23</f>
         <v/>
       </c>
       <c r="G25" s="5">
-        <f>G17/G20</f>
+        <f>G15/G23</f>
         <v/>
       </c>
       <c r="H25" s="5">
-        <f>H17/H20</f>
+        <f>H15/H23</f>
         <v/>
       </c>
       <c r="I25" s="5">
-        <f>I17/I20</f>
+        <f>I15/I23</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  % Cho vay Margin / Tổng DT</t>
+        </is>
+      </c>
+      <c r="B26" s="5">
+        <f>B16/B23</f>
+        <v/>
+      </c>
+      <c r="C26" s="5">
+        <f>C16/C23</f>
+        <v/>
+      </c>
+      <c r="D26" s="5">
+        <f>D16/D23</f>
+        <v/>
+      </c>
+      <c r="E26" s="5">
+        <f>E16/E23</f>
+        <v/>
+      </c>
+      <c r="F26" s="5">
+        <f>F16/F23</f>
+        <v/>
+      </c>
+      <c r="G26" s="5">
+        <f>G16/G23</f>
+        <v/>
+      </c>
+      <c r="H26" s="5">
+        <f>H16/H23</f>
+        <v/>
+      </c>
+      <c r="I26" s="5">
+        <f>I16/I23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  % Tự doanh (FVTPL) / Tổng DT</t>
+        </is>
+      </c>
+      <c r="B27" s="5">
+        <f>B17/B23</f>
+        <v/>
+      </c>
+      <c r="C27" s="5">
+        <f>C17/C23</f>
+        <v/>
+      </c>
+      <c r="D27" s="5">
+        <f>D17/D23</f>
+        <v/>
+      </c>
+      <c r="E27" s="5">
+        <f>E17/E23</f>
+        <v/>
+      </c>
+      <c r="F27" s="5">
+        <f>F17/F23</f>
+        <v/>
+      </c>
+      <c r="G27" s="5">
+        <f>G17/G23</f>
+        <v/>
+      </c>
+      <c r="H27" s="5">
+        <f>H17/H23</f>
+        <v/>
+      </c>
+      <c r="I27" s="5">
+        <f>I17/I23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  % IB + Lưu ký / Tổng DT</t>
+        </is>
+      </c>
+      <c r="B28" s="5">
+        <f>B20/B23</f>
+        <v/>
+      </c>
+      <c r="C28" s="5">
+        <f>C20/C23</f>
+        <v/>
+      </c>
+      <c r="D28" s="5">
+        <f>D20/D23</f>
+        <v/>
+      </c>
+      <c r="E28" s="5">
+        <f>E20/E23</f>
+        <v/>
+      </c>
+      <c r="F28" s="5">
+        <f>F20/F23</f>
+        <v/>
+      </c>
+      <c r="G28" s="5">
+        <f>G20/G23</f>
+        <v/>
+      </c>
+      <c r="H28" s="5">
+        <f>H20/H23</f>
+        <v/>
+      </c>
+      <c r="I28" s="5">
+        <f>I20/I23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
           <t xml:space="preserve">  % Quản lý quỹ / Tổng DT</t>
         </is>
       </c>
-      <c r="B26" s="5">
-        <f>B18/B20</f>
-        <v/>
-      </c>
-      <c r="C26" s="5">
-        <f>C18/C20</f>
-        <v/>
-      </c>
-      <c r="D26" s="5">
-        <f>D18/D20</f>
-        <v/>
-      </c>
-      <c r="E26" s="5">
-        <f>E18/E20</f>
-        <v/>
-      </c>
-      <c r="F26" s="5">
-        <f>F18/F20</f>
-        <v/>
-      </c>
-      <c r="G26" s="5">
-        <f>G18/G20</f>
-        <v/>
-      </c>
-      <c r="H26" s="5">
-        <f>H18/H20</f>
-        <v/>
-      </c>
-      <c r="I26" s="5">
-        <f>I18/I20</f>
+      <c r="B29" s="5">
+        <f>B21/B23</f>
+        <v/>
+      </c>
+      <c r="C29" s="5">
+        <f>C21/C23</f>
+        <v/>
+      </c>
+      <c r="D29" s="5">
+        <f>D21/D23</f>
+        <v/>
+      </c>
+      <c r="E29" s="5">
+        <f>E21/E23</f>
+        <v/>
+      </c>
+      <c r="F29" s="5">
+        <f>F21/F23</f>
+        <v/>
+      </c>
+      <c r="G29" s="5">
+        <f>G21/G23</f>
+        <v/>
+      </c>
+      <c r="H29" s="5">
+        <f>H21/H23</f>
+        <v/>
+      </c>
+      <c r="I29" s="5">
+        <f>I21/I23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>── CHI PHÍ THEO MẢNG (giá vốn, tỷ VND) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>(1) Chi phí Môi giới</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="n">
+        <v>-570.7</v>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>-429.3</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>-437.1</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>-595.8</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>-726.7</v>
+      </c>
+      <c r="G31" s="13">
+        <f>G15*'02_Assumptions'!G36</f>
+        <v/>
+      </c>
+      <c r="H31" s="13">
+        <f>H15*'02_Assumptions'!H36</f>
+        <v/>
+      </c>
+      <c r="I31" s="13">
+        <f>I15*'02_Assumptions'!I36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>(2) Chi phí lãi vay (giá vốn Margin)</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>-330.8</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>-477.4</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>-562.6</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>-764.1</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>-801.9</v>
+      </c>
+      <c r="G32" s="13">
+        <f>G10*'02_Assumptions'!G37</f>
+        <v/>
+      </c>
+      <c r="H32" s="13">
+        <f>H10*'02_Assumptions'!H37</f>
+        <v/>
+      </c>
+      <c r="I32" s="13">
+        <f>I10*'02_Assumptions'!I37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>(3) Chi phí hoạt động Tự doanh</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>-30.2</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>-40.2</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>-49.9</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>-43.4</v>
+      </c>
+      <c r="G33" s="13">
+        <f>G7*'02_Assumptions'!G38</f>
+        <v/>
+      </c>
+      <c r="H33" s="13">
+        <f>H7*'02_Assumptions'!H38</f>
+        <v/>
+      </c>
+      <c r="I33" s="13">
+        <f>I7*'02_Assumptions'!I38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>(4) Chi phí IB + Lưu ký</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>-68.59999999999999</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>-49.4</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>-89.90000000000001</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>-80.09999999999999</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>-84.59999999999999</v>
+      </c>
+      <c r="G34" s="13">
+        <f>G20*'02_Assumptions'!G39</f>
+        <v/>
+      </c>
+      <c r="H34" s="13">
+        <f>H20*'02_Assumptions'!H39</f>
+        <v/>
+      </c>
+      <c r="I34" s="13">
+        <f>I20*'02_Assumptions'!I39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>── LỢI NHUẬN GỘP THEO MẢNG (tỷ VND, KHÔNG gồm QLQ) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>LNG Môi giới</t>
+        </is>
+      </c>
+      <c r="B36" s="13">
+        <f>B15+B31</f>
+        <v/>
+      </c>
+      <c r="C36" s="13">
+        <f>C15+C31</f>
+        <v/>
+      </c>
+      <c r="D36" s="13">
+        <f>D15+D31</f>
+        <v/>
+      </c>
+      <c r="E36" s="13">
+        <f>E15+E31</f>
+        <v/>
+      </c>
+      <c r="F36" s="13">
+        <f>F15+F31</f>
+        <v/>
+      </c>
+      <c r="G36" s="13">
+        <f>G15+G31</f>
+        <v/>
+      </c>
+      <c r="H36" s="13">
+        <f>H15+H31</f>
+        <v/>
+      </c>
+      <c r="I36" s="13">
+        <f>I15+I31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>LNG Cho vay Margin</t>
+        </is>
+      </c>
+      <c r="B37" s="13">
+        <f>B16+B32</f>
+        <v/>
+      </c>
+      <c r="C37" s="13">
+        <f>C16+C32</f>
+        <v/>
+      </c>
+      <c r="D37" s="13">
+        <f>D16+D32</f>
+        <v/>
+      </c>
+      <c r="E37" s="13">
+        <f>E16+E32</f>
+        <v/>
+      </c>
+      <c r="F37" s="13">
+        <f>F16+F32</f>
+        <v/>
+      </c>
+      <c r="G37" s="13">
+        <f>G16+G32</f>
+        <v/>
+      </c>
+      <c r="H37" s="13">
+        <f>H16+H32</f>
+        <v/>
+      </c>
+      <c r="I37" s="13">
+        <f>I16+I32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>LNG Tự doanh (FVTPL+AFS)</t>
+        </is>
+      </c>
+      <c r="B38" s="13">
+        <f>B17+B33</f>
+        <v/>
+      </c>
+      <c r="C38" s="13">
+        <f>C17+C33</f>
+        <v/>
+      </c>
+      <c r="D38" s="13">
+        <f>D17+D33</f>
+        <v/>
+      </c>
+      <c r="E38" s="13">
+        <f>E17+E33</f>
+        <v/>
+      </c>
+      <c r="F38" s="13">
+        <f>F17+F33</f>
+        <v/>
+      </c>
+      <c r="G38" s="13">
+        <f>G17+G33</f>
+        <v/>
+      </c>
+      <c r="H38" s="13">
+        <f>H17+H33</f>
+        <v/>
+      </c>
+      <c r="I38" s="13">
+        <f>I17+I33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>LNG IB + Lưu ký</t>
+        </is>
+      </c>
+      <c r="B39" s="13">
+        <f>B20+B34</f>
+        <v/>
+      </c>
+      <c r="C39" s="13">
+        <f>C20+C34</f>
+        <v/>
+      </c>
+      <c r="D39" s="13">
+        <f>D20+D34</f>
+        <v/>
+      </c>
+      <c r="E39" s="13">
+        <f>E20+E34</f>
+        <v/>
+      </c>
+      <c r="F39" s="13">
+        <f>F20+F34</f>
+        <v/>
+      </c>
+      <c r="G39" s="13">
+        <f>G20+G34</f>
+        <v/>
+      </c>
+      <c r="H39" s="13">
+        <f>H20+H34</f>
+        <v/>
+      </c>
+      <c r="I39" s="13">
+        <f>I20+I34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>TỔNG LNG 4 MẢNG (không gồm QLQ)</t>
+        </is>
+      </c>
+      <c r="B40" s="29">
+        <f>B36+B37+B38+B39</f>
+        <v/>
+      </c>
+      <c r="C40" s="29">
+        <f>C36+C37+C38+C39</f>
+        <v/>
+      </c>
+      <c r="D40" s="29">
+        <f>D36+D37+D38+D39</f>
+        <v/>
+      </c>
+      <c r="E40" s="29">
+        <f>E36+E37+E38+E39</f>
+        <v/>
+      </c>
+      <c r="F40" s="29">
+        <f>F36+F37+F38+F39</f>
+        <v/>
+      </c>
+      <c r="G40" s="29">
+        <f>G36+G37+G38+G39</f>
+        <v/>
+      </c>
+      <c r="H40" s="29">
+        <f>H36+H37+H38+H39</f>
+        <v/>
+      </c>
+      <c r="I40" s="29">
+        <f>I36+I37+I38+I39</f>
         <v/>
       </c>
     </row>
@@ -18448,22 +19578,22 @@
         <v>4980.2</v>
       </c>
       <c r="G2" s="13">
-        <f>'03_Revenue_Model'!G20</f>
+        <f>'03_Revenue_Model'!G23</f>
         <v/>
       </c>
       <c r="H2" s="13">
-        <f>'03_Revenue_Model'!H20</f>
+        <f>'03_Revenue_Model'!H23</f>
         <v/>
       </c>
       <c r="I2" s="13">
-        <f>'03_Revenue_Model'!I20</f>
+        <f>'03_Revenue_Model'!I23</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Chi phí hoạt động</t>
+          <t>Chi phí hoạt động (= tổng chi phí 4 mảng bottom-up)</t>
         </is>
       </c>
       <c r="B3" s="13" t="n">
@@ -18482,15 +19612,15 @@
         <v>-2391</v>
       </c>
       <c r="G3" s="13">
-        <f>-G2*'02_Assumptions'!G36</f>
+        <f>SUM('03_Revenue_Model'!G31:G34)</f>
         <v/>
       </c>
       <c r="H3" s="13">
-        <f>-H2*'02_Assumptions'!H36</f>
+        <f>SUM('03_Revenue_Model'!H31:H34)</f>
         <v/>
       </c>
       <c r="I3" s="13">
-        <f>-I2*'02_Assumptions'!I36</f>
+        <f>SUM('03_Revenue_Model'!I31:I34)</f>
         <v/>
       </c>
     </row>
@@ -18555,15 +19685,15 @@
         <v>-144.9</v>
       </c>
       <c r="G5" s="13">
-        <f>-G2*'02_Assumptions'!G37</f>
+        <f>-G2*'02_Assumptions'!G42</f>
         <v/>
       </c>
       <c r="H5" s="13">
-        <f>-H2*'02_Assumptions'!H37</f>
+        <f>-H2*'02_Assumptions'!H42</f>
         <v/>
       </c>
       <c r="I5" s="13">
-        <f>-I2*'02_Assumptions'!I37</f>
+        <f>-I2*'02_Assumptions'!I42</f>
         <v/>
       </c>
     </row>
@@ -18623,15 +19753,15 @@
         <v>-287.3</v>
       </c>
       <c r="G7" s="13">
-        <f>-MAX(G6,0)*'02_Assumptions'!G38</f>
+        <f>-MAX(G6,0)*'02_Assumptions'!G43</f>
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>-MAX(H6,0)*'02_Assumptions'!H38</f>
+        <f>-MAX(H6,0)*'02_Assumptions'!H43</f>
         <v/>
       </c>
       <c r="I7" s="13">
-        <f>-MAX(I6,0)*'02_Assumptions'!I38</f>
+        <f>-MAX(I6,0)*'02_Assumptions'!I43</f>
         <v/>
       </c>
     </row>
@@ -18978,7 +20108,7 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>'03_Revenue_Model'!G12+'03_Revenue_Model'!G13+'03_Revenue_Model'!G14+'03_Revenue_Model'!G17+'03_Revenue_Model'!G18</f>
+        <f>'03_Revenue_Model'!G15+'03_Revenue_Model'!G16+'03_Revenue_Model'!G17+'03_Revenue_Model'!G20+'03_Revenue_Model'!G21</f>
         <v/>
       </c>
       <c r="C10" s="13">
@@ -19410,13 +20540,13 @@
         <v>16064.5</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>22424.7</v>
+        <v>22641.1</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>25529.7</v>
+        <v>26253.6</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>28013.6</v>
+        <v>29279.5</v>
       </c>
     </row>
     <row r="8">
@@ -19511,13 +20641,13 @@
         <v>18009.9</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>19183.1</v>
+        <v>18966.7</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>20238.1</v>
+        <v>19514.3</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>21369.3</v>
+        <v>20103.3</v>
       </c>
     </row>
     <row r="12">
